--- a/EverAfter-Wedding-Budget-Suite.xlsx
+++ b/EverAfter-Wedding-Budget-Suite.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,84 +34,96 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="005D2E46"/>
-      <sz val="18"/>
+      <color rgb="005d2e46"/>
+      <sz val="24"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00B87D6D"/>
+      <color rgb="00b87d6d"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="005D2E46"/>
-      <sz val="11"/>
+      <color rgb="005d2e46"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="005D2E46"/>
-      <sz val="20"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00B87D6D"/>
+      <color rgb="00b87d6d"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B87D6D"/>
+      <color rgb="00d4a5a5"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="005D2E46"/>
-      <sz val="16"/>
+      <color rgb="005d2e46"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00B87D6D"/>
+      <color rgb="00b87d6d"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="005d2e46"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="005D2E46"/>
+      <b val="1"/>
+      <color rgb="00e8d5c4"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00ffffff"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="005d2e46"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00b87d6d"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="005d2e46"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="005D2E46"/>
+      <color rgb="005d2e46"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00ffffff"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00ffffff"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B87D6D"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="11">
@@ -123,60 +135,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF6F1"/>
-        <bgColor rgb="00FAF6F1"/>
+        <fgColor rgb="00faf6f1"/>
+        <bgColor rgb="00faf6f1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5C4"/>
-        <bgColor rgb="00E8D5C4"/>
+        <fgColor rgb="00b87d6d"/>
+        <bgColor rgb="00b87d6d"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00ffffff"/>
+        <bgColor rgb="00ffffff"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B87D6D"/>
-        <bgColor rgb="00B87D6D"/>
+        <fgColor rgb="00d4a5a5"/>
+        <bgColor rgb="00d4a5a5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005D2E46"/>
-        <bgColor rgb="005D2E46"/>
+        <fgColor rgb="005d2e46"/>
+        <bgColor rgb="005d2e46"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00e8d5c4"/>
+        <bgColor rgb="00e8d5c4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00d4edda"/>
+        <bgColor rgb="00d4edda"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
-        <bgColor rgb="00D1ECF1"/>
+        <fgColor rgb="00fff3cd"/>
+        <bgColor rgb="00fff3cd"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4A5A5"/>
-        <bgColor rgb="00D4A5A5"/>
+        <fgColor rgb="00d1ecf1"/>
+        <bgColor rgb="00d1ecf1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -184,107 +196,303 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00e8d5c4"/>
+      </left>
+      <top style="thin">
+        <color rgb="00e8d5c4"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00e8d5c4"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00e8d5c4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00e8d5c4"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00e8d5c4"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00e8d5c4"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00e8d5c4"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="00e8d5c4"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00d4a5a5"/>
+      </left>
+      <top style="thin">
+        <color rgb="00e8d5c4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00d4a5a5"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00b87d6d"/>
+      </left>
+      <top style="thin">
+        <color rgb="00e8d5c4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00b87d6d"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="005d2e46"/>
+      </left>
+      <top style="thin">
+        <color rgb="00e8d5c4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="005d2e46"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00e8d5c4"/>
+      </left>
+      <top style="thin">
+        <color rgb="00e8d5c4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00e8d5c4"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00e8d5c4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -648,25 +856,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00B87D6D"/>
+    <tabColor rgb="00b87d6d"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EverAfter — Wedding Budget Suite</t>
+          <t>EverAfter</t>
         </is>
       </c>
     </row>
@@ -677,286 +891,895 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>WEDDING COUNTDOWN</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WEDDING COUNTDOWN</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>DAYS</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>HOURS</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>MINUTES</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>BUDGET SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="13" t="n"/>
+    </row>
+    <row r="8" ht="12" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Total Budget</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Committed</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>$50,000</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>$42,350</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>$28,100</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>$7,650</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="20" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Original estimate</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>84.7% allocated</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>56.2% of budget</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="27" t="inlineStr">
         <is>
           <t>Available to spend</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>UPCOMING PAYMENTS</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>RECENT ACTIVITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="13" t="n"/>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  UPCOMING PAYMENTS</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECENT ACTIVITY</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Due Date</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="28" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="L14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Photography</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Due in 2 days</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>2 days</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>$3,200</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>Today, 9:30 AM</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>Final guest count confirmed</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="34" t="inlineStr">
         <is>
           <t>142 attending (was 150)</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="L15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Florist</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Due in 5 days</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>5 days</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>$2,800</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>Yesterday</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>Seating chart finalized</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="34" t="inlineStr">
         <is>
           <t>Saved $400 by reducing table count</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="L16" s="13" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Transportation</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Due in 8 days</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>8 days</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>$1,200</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>Jun 8</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>Catering headcount due</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="34" t="inlineStr">
         <is>
           <t>Pending — waiting on 3 RSVPs</t>
         </is>
       </c>
+      <c r="L17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
+  <mergeCells count="35">
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="J9:L9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -965,11 +1788,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00D4A5A5"/>
+    <tabColor rgb="00d4a5a5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -977,230 +1800,645 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>BUDGET BREAKDOWN</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>All wedding budget categories and spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="36" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="36" t="n"/>
+      <c r="D3" s="36" t="n"/>
+      <c r="E3" s="36" t="n"/>
+      <c r="F3" s="36" t="n"/>
+      <c r="G3" s="36" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Spent</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>% Used</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Venue &amp; Rentals</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Grandview Estate, chairs, tables, linens</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C6" s="38" t="n">
         <v>15000</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D6" s="39" t="n">
         <v>15000</v>
       </c>
-      <c r="E4" s="17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="E6" s="40">
+        <f>D6/C6</f>
+        <v/>
+      </c>
+      <c r="F6" s="38">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="G6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>Catering &amp; Bar</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>$105 per person × 142 guests</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C7" s="43" t="n">
         <v>15000</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D7" s="44" t="n">
         <v>14910</v>
       </c>
-      <c r="E5" s="22" t="n">
-        <v>0.994</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="E7" s="45">
+        <f>D7/C7</f>
+        <v/>
+      </c>
+      <c r="F7" s="43">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="G7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>Photography &amp; Video</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>8 hours coverage, 2 shooters</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C8" s="38" t="n">
         <v>6000</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D8" s="39" t="n">
         <v>4800</v>
       </c>
-      <c r="E6" s="17" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="E8" s="40">
+        <f>D8/C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="38">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="G8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Florist &amp; Decor</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>Bouquets, centerpieces, arch</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C9" s="43" t="n">
         <v>4000</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D9" s="44" t="n">
         <v>3000</v>
       </c>
-      <c r="E7" s="22" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="E9" s="45">
+        <f>D9/C9</f>
+        <v/>
+      </c>
+      <c r="F9" s="43">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="G9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>Music &amp; Entertainment</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>DJ + live ceremony quartet</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C10" s="38" t="n">
         <v>3000</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D10" s="39" t="n">
         <v>1800</v>
       </c>
-      <c r="E8" s="17" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="E10" s="40">
+        <f>D10/C10</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="G10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>Attire &amp; Beauty</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>Dress, suit, alterations, hair &amp; makeup</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C11" s="43" t="n">
         <v>3000</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D11" s="44" t="n">
         <v>2700</v>
       </c>
-      <c r="E9" s="22" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="E11" s="45">
+        <f>D11/C11</f>
+        <v/>
+      </c>
+      <c r="F11" s="43">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="G11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>Stationery &amp; Gifts</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Invites, programs, favors</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C12" s="38" t="n">
         <v>1300</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D12" s="39" t="n">
         <v>650</v>
       </c>
-      <c r="E10" s="17" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="E12" s="40">
+        <f>D12/C12</f>
+        <v/>
+      </c>
+      <c r="F12" s="38">
+        <f>C12-D12</f>
+        <v/>
+      </c>
+      <c r="G12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Miscellaneous</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>Tips, emergency fund, marriage license</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C13" s="43" t="n">
         <v>1700</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D13" s="44" t="n">
         <v>490</v>
       </c>
-      <c r="E11" s="22" t="n">
-        <v>0.288</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="E13" s="45">
+        <f>D13/C13</f>
+        <v/>
+      </c>
+      <c r="F13" s="43">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="G13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n">
-        <v>49000</v>
-      </c>
-      <c r="D12" s="24" t="n">
-        <v>43350</v>
-      </c>
-      <c r="E12" s="25" t="n">
-        <v>0.8846938775510204</v>
-      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="47">
+        <f>SUM(C6:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="47">
+        <f>SUM(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="48">
+        <f>D14/C14</f>
+        <v/>
+      </c>
+      <c r="F14" s="47">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="3">
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1209,183 +2447,486 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00E8D5C4"/>
+    <tabColor rgb="00e8d5c4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>VENDOR TRACKER</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>All wedding vendors and booking status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="49" t="n"/>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Grandview Estate</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Deposit paid, final due 2 weeks before</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>Lumiere Photography</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>Photography</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>8 hours, 2 shooters</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>Harvest Table Catering</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Catering</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C8" s="51" t="inlineStr">
         <is>
           <t>Booked</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>142 guests, $105/head</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Petal &amp; Stem</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>Florist</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Awaiting final quote</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>Soundwave DJs</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C10" s="54" t="inlineStr">
         <is>
           <t>Quoted</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>DJ + ceremony quartet package</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>Napa Classic Cars</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B11" s="52" t="inlineStr">
         <is>
           <t>Transportation</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C11" s="54" t="inlineStr">
         <is>
           <t>Quoted</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Vintage Rolls option</t>
         </is>
       </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1394,263 +2935,642 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="005D2E46"/>
+    <tabColor rgb="005d2e46"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>GUEST LIST</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>SUMMARY</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>GUEST DETAILS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Wedding guest management</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="55" t="n"/>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+      <c r="F3" s="55" t="n"/>
+      <c r="G3" s="55" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GUEST SUMMARY</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GUEST DETAILS</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Invited</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B6" s="31" t="n">
         <v>200</v>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>Dietary</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>Attending</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B7" s="57" t="n">
         <v>142</v>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="C7" s="58" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>Eleanor &amp; Robert Whitfield</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F7" s="52" t="inlineStr">
         <is>
           <t>Attending</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G7" s="42" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Declined</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B8" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>Marcus Chen</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>Friend</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Attending</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>Vegetarian</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B9" s="57" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="C9" s="58" t="n"/>
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>Alexandra Ross</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>Friend</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F9" s="52" t="inlineStr">
         <is>
           <t>Attending</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G9" s="42" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Cost Per Head</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>$148</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>David &amp; Susan Park</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E10" s="59" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Attending</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G10" s="34" t="inlineStr">
         <is>
           <t>Gluten-free</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="D9" s="18" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="41" t="inlineStr">
         <is>
           <t>Jennifer Blake</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F11" s="52" t="inlineStr">
         <is>
           <t>Attending</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G11" s="42" t="inlineStr">
         <is>
           <t>Vegan</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="D10" s="10" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>Thomas &amp; Marie Laurent</t>
         </is>
       </c>
-      <c r="E10" s="31" t="inlineStr">
+      <c r="E12" s="59" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>Declined</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="D11" s="18" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="41" t="inlineStr">
         <is>
           <t>Jordan Smith</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>Friend</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F13" s="52" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G13" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D3:F3"/>
+  <mergeCells count="4">
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1659,205 +3579,502 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00B87D6D"/>
+    <tabColor rgb="00b87d6d"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>WEDDING DAY TIMELINE</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>June 14, 2026 — Grandview Estate, Napa Valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>Location / Notes</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Hair &amp; Makeup</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>Bridal suite — 4 artists on site</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Photographer Arrives</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>Detail shots, getting-ready candids</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>First Look</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>Garden terrace — private moment</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t>2:30 PM</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Ceremony</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>Grandview lawn — 30 minutes</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Cocktail Hour</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>Terrace &amp; garden — passed hors d'oeuvres</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D10" s="63" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>4:30 PM</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Reception</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C11" s="42" t="inlineStr">
         <is>
           <t>Grand ballroom — dinner, speeches, dancing</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D11" s="63" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>10:00 PM</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Sparkler Send-off</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Front circle drive</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D12" s="63" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
       </c>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
